--- a/data/google_news_dedup_28_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_28_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Voordeur en geparkeerde wagen beschadigd bij aanslag in Antwerpen-Noord - Nieuwsblad</t>
+          <t>Arbeider in kritieke toestand na zware explosie bij tuinbouwbedrijf in Duffel - HLN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Front door and parked car damaged in attack in Antwerp North - Nieuwsblad</t>
+          <t>Worker in critical condition after major explosion at horticultural company in Duffel - HLN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 10:55:29 GMT</t>
+          <t>Tue, 28 Apr 2026 14:01:52 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxONjNzZ0wxZXFwTFpZMmYzaEhHLWlyZWdxbTFRN0N3QzFyZjVfVkpkdExHZy1KTVJwclNLVDVRRS1qRHFQSHJabFZKQUg0NmN0NW5HRFp3T0hRY0VtUW9namoxRXQ4ZEZJNVFxaU8yU25oQmwxREVRT2lZZVlEcjF4NXlycWN2Q1ZhY2VBODRaaWRaY25Ma0hPXzhabzhKa1VQeTV2VWJGV2FfODBlQVRhcjZ3Y25vZVBrak1OWHZDOXIwZXZJSkJfbVo0RVRhNFNPU2gxRlJwbk5RT3FFWDN0MWdsbEdhVVpsTUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPUzdseVFsYnd1VDhpVU5MQXA1dlZkZHJPSDFHTFZMSFk0Vjh2Qnoyb1ZzZmcyYV91ODJlM0FMVlNJRU9BOTBScTVwRVAwSmdHcmJMREQ2djZTUFRvZDJQcl9fMEpnWFZnbWJDWGFEUEVtZEdTc1VBS3pRWUo0VkF2azFGS0V0b3RVNjlzUG14RW9nVnRpTG1rRWhFM3c0Ym43TzhRNUZ4ckx2cGltalVFMzhPSQ?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46140.45519675926</v>
+        <v>46140.58462962963</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ex-voetbaltrainer uit Edegem veroordeeld tot 8 jaar cel en 5 jaar tbs voor zedenfeiten met minderjarigen - HLN</t>
+          <t>Voordeur en geparkeerde wagen beschadigd bij aanslag in Antwerpen-Noord - Nieuwsblad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ex-football coach from Edegem sentenced to 8 years in prison and 5 years of TBS for sexual offenses with minors - HLN</t>
+          <t>Front door and parked car damaged in attack in Antwerp North - Nieuwsblad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 09:31:07 GMT</t>
+          <t>Tue, 28 Apr 2026 10:55:29 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSndtSnVjSUtlMFowb24wd1dRd29ZMTZPZV80aU1BWmJUVjZkQTlEYUE5VEpiUFFJQ2pTMTg5dGRpbXEzYm1GMFVMbGtsTWI1b1lxQU9OX0hBMlhERjdRMEtHX3ppbi1iMzV2WmxvMjhLUWFQQ05OazJOOEJlcU8tSDNpcnVQbzFudjVkWW0yOFA4VDVISEpSUExSc0REOXVrVjBjdzZOZUVjTm1UTmt6eHpGdm5yNE9xSDQ2WTNKZDBvLW1kLWtITGV1YXF1YmM1OFY0ZE96UDMyZXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxONjNzZ0wxZXFwTFpZMmYzaEhHLWlyZWdxbTFRN0N3QzFyZjVfVkpkdExHZy1KTVJwclNLVDVRRS1qRHFQSHJabFZKQUg0NmN0NW5HRFp3T0hRY0VtUW9namoxRXQ4ZEZJNVFxaU8yU25oQmwxREVRT2lZZVlEcjF4NXlycWN2Q1ZhY2VBODRaaWRaY25Ma0hPXzhabzhKa1VQeTV2VWJGV2FfODBlQVRhcjZ3Y25vZVBrak1OWHZDOXIwZXZJSkJfbVo0RVRhNFNPU2gxRlJwbk5RT3FFWDN0MWdsbEdhVVpsTUE?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46140.3966087963</v>
+        <v>46140.45519675926</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hij moet hier nog 8 jaar naar cel voor gijzeling van restauranthouder: Antwerpenaar ‘Popeye’ (40) opgepakt in Dubai - GVA</t>
+          <t>Ex-voetbaltrainer uit Edegem veroordeeld tot 8 jaar cel en 5 jaar tbs voor zedenfeiten met minderjarigen - HLN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>He has to go to prison for another 8 years for taking restaurant owner hostage: Antwerp resident 'Popeye' (40) arrested in Dubai - GVA</t>
+          <t>Ex-football coach from Edegem sentenced to 8 years in prison and 5 years of TBS for sexual offenses with minors - HLN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 10:21:29 GMT</t>
+          <t>Tue, 28 Apr 2026 09:31:07 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxQY2pESHJ5Ny10eVlGRmNmMVhfUnUzWlFiLWVfR2JLajZfUXlEMzc1ZmhOcXladmZmaGQ2X2xiWU5tY2NsRkJvalZBMGMzaVN0eWVRRzBPaVZkRHZkWHZ4WmprcDgyNHVIdUpLT2VnOUZncmJXenZCRC1LcjgzVjN2MGhTMVpfd1cxTGVKTFlDVnZPMlVib2NkdlVFcHNtUDk5TTFEMnBsQjlFdVhjRnVPWGk5cTFCcXBsN2RIdEhBcUUtb2VxR2RSbWRheUt5d1Fsc29rYXNRNFJiVDh0Rjd6M1FZTWlQRUpqcUdNTmo1Q28wRTZfMGtmQ1EzOTZVZm9GNTFWRmc3dFNlVVlrQW5qVVZaUjI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNSndtSnVjSUtlMFowb24wd1dRd29ZMTZPZV80aU1BWmJUVjZkQTlEYUE5VEpiUFFJQ2pTMTg5dGRpbXEzYm1GMFVMbGtsTWI1b1lxQU9OX0hBMlhERjdRMEtHX3ppbi1iMzV2WmxvMjhLUWFQQ05OazJOOEJlcU8tSDNpcnVQbzFudjVkWW0yOFA4VDVISEpSUExSc0REOXVrVjBjdzZOZUVjTm1UTmt6eHpGdm5yNE9xSDQ2WTNKZDBvLW1kLWtITGV1YXF1YmM1OFY0ZE96UDMyZXc?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46140.43158564815</v>
+        <v>46140.3966087963</v>
       </c>
     </row>
     <row r="10">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Flights resume in Kuwait as airspace reopens after Iran war disruption - Travel Tomorrow</t>
+          <t>Jet fuel crisis puts passenger rights to the test as cancellations rise - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Flights resume in Kuwait as airspace reopens after Iran war disruption - Travel Tomorrow</t>
+          <t>Jet fuel crisis puts passenger rights to the test as cancellations rise - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 10:35:18 GMT</t>
+          <t>Tue, 28 Apr 2026 13:50:49 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSVhsdnpfVWtyZXU1elJ4dnp0eGVJcEcyVHBqZGxNZEVlZndQQUF5TEFzYnYzUXZSOUlIRmZXbWkyc2w0T1U3RllmX1dXX0ZhZ2lSMGFMZ1pUNjlCWW1JNXNNWDFXMERrd2U3Sm90X0ZfTW1xcUFlcG5kUnhwWlRwX0NMODI0anJCMGJkRFRYUC11VHZ2bEY0N0pUZDdSV00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPaUVQRFE2ZFZia3oxZGY5MzlmWm1qUmdQOXA1SXhseDhIdWZoSXZxZlk4Yy1xWTBzZXZQbjVaNVc3cW93QmtWUnh0WExvOVFHVUVvbWQ2TnVkYmRRQXJWX0k2T2ZGeTV2Y2pOYnpLX2lKdS1OYkxuN1dwSGdSaFBWaVZ0MVhRdUNvYzFzYU5wZzZMSHNvNkdubG5MYzFMWUhL?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46140.44118055556</v>
+        <v>46140.57695601852</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Does Europe’s Climate Democracy Face An Age Problem? From Brussels to Athens - tovima.com</t>
+          <t>Flights resume in Kuwait as airspace reopens after Iran war disruption - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Does Europe’s Climate Democracy Face An Age Problem? From Brussels to Athens - tovima.com</t>
+          <t>Flights resume in Kuwait as airspace reopens after Iran war disruption - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 07:02:54 GMT</t>
+          <t>Tue, 28 Apr 2026 10:35:18 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPYmI5TVVNZERWWXM1eVByTlVheTVqeWtCYlhEODQ0TTV5YXkwcWRhQkdRYWdYTW1Mc1pQSWQzQUxfMnRfZ0VGZmJ0a2RuRmk3YURmdTlBZjZyekhZX3g3WGkweFBqVXM4Rm41andPMWoyQ2FRa3hjNDFiajF3aTc5cnlhV0t0SU5XeXZoUDJCUXg4MGRraUl5QU04QmlwX2ctVTMyOGFDVE9XMGfSAbABQVVfeXFMTmczQ3pRU2FYZlJOU2JDZkpjNWl1Y25DZG01NHpuQVJreERnSUE3Y1hQVllieVZrOTdDZEVvRVh3eU9KeExEMXN5bnp4MjdLNGhORkRDQ1lTMHVOOGlIZE83WEZYWVVSbUtiZ093aE5JX0cwWi1fZ25wMUpnUEdCT0FDNWp1NmJOUDJYSExTSDdRWURWV1dzMWgtLVFReEFmSFhaRGVZSHl5UURGcm9MeEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSVhsdnpfVWtyZXU1elJ4dnp0eGVJcEcyVHBqZGxNZEVlZndQQUF5TEFzYnYzUXZSOUlIRmZXbWkyc2w0T1U3RllmX1dXX0ZhZ2lSMGFMZ1pUNjlCWW1JNXNNWDFXMERrd2U3Sm90X0ZfTW1xcUFlcG5kUnhwWlRwX0NMODI0anJCMGJkRFRYUC11VHZ2bEY0N0pUZDdSV00?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46140.29368055556</v>
+        <v>46140.44118055556</v>
       </c>
     </row>
     <row r="14">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Des chercheurs belges mettent au point une avancée majeure pour mieux identifier des agresseurs sexuels grâce à l'ADN - BruxellesToday</t>
+          <t>Affaire Patrick Bruel : Aurore Bergé appelle à respecter la parole des victimes et la présomption d’innocence - Charente Libre</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Belgian researchers develop a major breakthrough to better identify sexual attackers using DNA - BruxellesToday</t>
+          <t>Patrick Bruel affair: Aurore Bergé calls for respecting the words of victims and the presumption of innocence - Charente Libre</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 07:35:00 GMT</t>
+          <t>Tue, 28 Apr 2026 08:29:45 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNWm1yMUtBeE9pcmdDUnNkMkQ3T1dWMGZyYjIwT3Q5VExGQnZQZXdZSUlxdWROM0pNTnR1WmdsbVpxNVI2NXVIdjRGTWJYY1VPQkRCcmUtbnFmbDYwVHZJak9VQ2htM2xPWUsyN290NnpObHhJcGJhNTRzNTZ1Uld5MFZkMHdkSDRGX3pkSmJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQVGc2alJpdUV4b0ZFNnpaMWVuYVNGSzd6VlBmTzNKU1RpY1VmcVRRVWtfenpiVUpzcDRhc2hMSWhSMV9SWlRzakZjWWNzdGNzMGRQckZkQWdMRkFjV2k0MklRc242UUxaUF9WQ1Q5eWM5RUthUzdwcVROdmtXNXFYSzl4TFA0N0puTUo2SFVUWFBwQ0V5dHVRdGozbkxJLTZWNUVybDlzemNjRmh3Z0NMMnk2Z3NzUHNVY1hRNUJSRjNTN0Zzcks4Yk85eFU0U3VvR3g2ay1kUndySEY0ODNuMHI0c0ZIc0lEaVIyMzBYQ3EtWVk5?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,38 +1189,38 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46140.31597222222</v>
+        <v>46140.35399305556</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Affaire Patrick Bruel : Aurore Bergé appelle à respecter la parole des victimes et la présomption d’innocence - Charente Libre</t>
+          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - CediRates</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Patrick Bruel affair: Aurore Bergé calls for respecting the words of victims and the presumption of innocence - Charente Libre</t>
+          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - CediRates</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 08:29:45 GMT</t>
+          <t>Tue, 28 Apr 2026 13:30:00 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQVGc2alJpdUV4b0ZFNnpaMWVuYVNGSzd6VlBmTzNKU1RpY1VmcVRRVWtfenpiVUpzcDRhc2hMSWhSMV9SWlRzakZjWWNzdGNzMGRQckZkQWdMRkFjV2k0MklRc242UUxaUF9WQ1Q5eWM5RUthUzdwcVROdmtXNXFYSzl4TFA0N0puTUo2SFVUWFBwQ0V5dHVRdGozbkxJLTZWNUVybDlzemNjRmh3Z0NMMnk2Z3NzUHNVY1hRNUJSRjNTN0Zzcks4Yk85eFU0U3VvR3g2ay1kUndySEY0ODNuMHI0c0ZIc0lEaVIyMzBYQ3EtWVk5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNU1hyZmlQdkpqQmljcjNIY21KenBnVHAzeFBOOC1hZ3BqU0xDYi1QczZHMXB1Vy1oSWptX0stMGtTWE1ZR1l0ZnRSb2dDbF82NDVuSWo1MGp4aHhSSWtnbFY4LXBJY3dRUGJYVk9wZUVHUnBYamZGMGZRSWFEQmdJYkZSVGViNXowSHJRNktubHM?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,52 +1230,52 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46140.35399305556</v>
+        <v>46140.5625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - CediRates</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Raymond Asante scores in Patro’s playoff defeat to Beerschot - CediRates</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 13:30:00 GMT</t>
+          <t>Tue, 28 Apr 2026 11:56:18 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNU1hyZmlQdkpqQmljcjNIY21KenBnVHAzeFBOOC1hZ3BqU0xDYi1QczZHMXB1Vy1oSWptX0stMGtTWE1ZR1l0ZnRSb2dDbF82NDVuSWo1MGp4aHhSSWtnbFY4LXBJY3dRUGJYVk9wZUVHUnBYamZGMGZRSWFEQmdJYkZSVGViNXowSHJRNktubHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxNVW9kUjlEZF9xZXZMRXNxRnFLejZrUEUzWWhfVFlDNjNQVWRPRG85ajkza0hKNF9PWmFORjN6emVtTEtHTFBxVFlFQmFWVmlqQVlKNW9Udlo0cnl2dGNLcmhkbWVaWG8xZzRsY3dXR1ZYVXllWlJYdWdUMW12eGQwZHJ2MUVsYnZsSDRuWm9GN1E2bmhOWWFlNDRnN2ViU1A4MEFLTl9YODBrTFAxMlktazhIVk5MWWRoSWJoZzRPMU8zNWFsMXk5TFhtenZRaElaempJOFR4Zk5kVEc2ZXFsXzl4MWF5VGhuVUFWZzlJUXpUbUlERlBLaEttbE5fOXNTRTAxV1ZpM0w2LTlDU3IzWm1LR0lkV19SY3pGbWdORUlGaTlQdGhpLW5SUFpnV2c4NzMyWmFHSVJERTh2d18yZ3VrTWI?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46140.5625</v>
+        <v>46140.49743055556</v>
       </c>
     </row>
     <row r="17">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>40 Räder bei Einbruch in Fahrradgeschäft gestohlen - Fränkischer Tag</t>
+          <t>Kriminalität: 40 Räder bei Einbruch in Fahrradgeschäft gestohlen - Neue Presse Coburg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40 bikes stolen in bike shop break-in - Franconian day</t>
+          <t>Crime: 40 bikes stolen in bike shop break-in - Neue Presse Coburg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 12:16:19 GMT</t>
+          <t>Tue, 28 Apr 2026 12:20:47 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPMURaUDIwTThlYVZtOXdMSGxhczlPNGdycUJIbTFyUzhXTkh6RE9Tc2kxTm5ZSjBvcTR3T3B1d2s3eHBBLU5kamUxVFE3VWJmdENYTWppby1ycF9DWlpJajBnT2JKa2xybmFwbkNxdVZMMnhUMS1nZThOZWJ6emlaNHhVV2NScmctWTRLTUswektlTDllNkR6dEtzajI0LUpNRjF4R0RYSlRjTHRfTHhDVWFsZkZzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQaTduN1g5bXJRX3hMLVZXZDB1X2RrZXU0V3haU2RNSDlXSFVyOXpMUzg0TGhacS1mYTFaQWE4R21GMjlscDdMQUNlUEhZWEN5MmJLS1laaENZVVA2NzUzaGFhd1BvMFJtUGd0NDZZWkFoSHZ2eXp5eEdFZHN1ejJpcnhkWHdaSHFSTDU3M2phZWE5ZlcxNS1fdWlObk4xM0dxdDRMY1V5akg5d3lGZGdnMGJyM3JTM3UzUXlrX2V2YVV2d0h1dzZ1VE45MmhhUW00WWtrSm1zWQ?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46140.51133101852</v>
+        <v>46140.51443287037</v>
       </c>
     </row>
     <row r="19">
@@ -1525,32 +1525,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
+          <t>Inside storybook cottage in upscale Kildare village on the market for €635K - MSN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
+          <t>Inside storybook cottage in upscale Kildare village on the market for €635K - MSN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 13:36:52 GMT</t>
+          <t>Tue, 28 Apr 2026 12:07:14 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRkNkcDkxV1hrOVVEeDBITjlqTHBncC1BT3NqMUVPLW9zaFEwbkpvWWZtZWdRUF9DUXVOWHpDcWR2UUJOblFyTzV3NVB1M25JaVlqUnhxbHB6Sm1Bb3FKZTdDT3M3dUp4ZldBd3M0T1p1azktanRzZE1VamN1dmNlVmVYa3VyVWhQdTQtcm5sR0w3TXhaOEg3ZWtJc2VKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNV3JObk9Kam84VUpxeXB3OUt0eWJsT1lyWWVZVV9VZlBUNjdlZUNiX0tUeXEwOXRWbVhHNUFYbXNRWU8tS1VhdTlzbWtLck9CakhXeEFkRzhyYl9JT3NZeC1xbmJEVXFKcC04bXJ5V0V6T0xPaTl1aVhsUUVlYlF4T2dvcFJ6am9vR1NLUjBuUDR6Q2wxeG9oZkdHaEdyVGR1NEdEUnlQT1AxWDBJSXgzTFE1UlN2NFVsS1VKUlVFX0NtRzFPSmZXY1AwTzNtRG5pZ0FoNDU5S2tqYzc5V3dGR1M2UFFxMmlFZHBn?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46140.56726851852</v>
+        <v>46140.50502314815</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pro-Palestinian protesters blockade defence factory in Edinburgh - London Now</t>
+          <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pro-Palestinian protesters blockade defence factory in Edinburgh - London Now</t>
+          <t>Man taken to hospital after stabbing near busy road in Leytonstone - Guardian Series</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 10:15:56 GMT</t>
+          <t>Tue, 28 Apr 2026 13:36:52 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGhRS2pSRTBfV254VWxvdXc1UEsxbHAxdVVsbHlhLXJQd1ZYTEU0QjNDcm9DRF9tZ0RkeUxQWHBGd0dDMkZKRFZhR3Ztdk1OQ1pGazJqSXJ5VUFrcFlyM0VVeUhyUGV0YUtQbXZwOWtQSV9JU3h1d1BWLW42dDJWd1Vxdm80d3NMdnNZM1Z0UVBtSHRqakNlNHE5MDNueU80UmlubUJkSEhIZXpReGYzU0tVNnA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRkNkcDkxV1hrOVVEeDBITjlqTHBncC1BT3NqMUVPLW9zaFEwbkpvWWZtZWdRUF9DUXVOWHpDcWR2UUJOblFyTzV3NVB1M25JaVlqUnhxbHB6Sm1Bb3FKZTdDT3M3dUp4ZldBd3M0T1p1azktanRzZE1VamN1dmNlVmVYa3VyVWhQdTQtcm5sR0w3TXhaOEg3ZWtJc2VKdw?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,38 +1629,38 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46140.42773148148</v>
+        <v>46140.56726851852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Corteo del 25 aprile: la Comunità ebraica di Milano chiede un chiarimento al sindaco Sala - mosaico-cem.it</t>
+          <t>King’s College London spent over £37,000 on protest-related legal advice - The Tab</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>March 25th procession: the Jewish community of Milan asks mayor Sala for clarification - mosaico-cem.it</t>
+          <t>King’s College London spent over £37,000 on protest-related legal advice - The Tab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 07:08:01 GMT</t>
+          <t>Tue, 28 Apr 2026 14:23:19 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNRTcwVXAwTHg2anVNNnRoSzZNdV94YVFkem41QkZ3V2tBQ0VGRDJqVWxia2dDM2FkZnAxVHZwMkZvZk5Vd0RmVkJvSEhidklib0F0aGhVNGkzemUxc1U4SG5NRjJtNFNYMGtjUjVlbXpleWdnNTBlT2dYYXZ1WVhnUUFmeHZSZFdtbWd6VU54Q0VvQnd5R2sxM3pfMHZoalhWWTBxU2pSeS1VaktSSHdEbUU0Z09SUHZVRHVHZVBmMkpXT1VSZ2QxZHYwV0RjSGdjem43TmtwZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPU0RDSk90VHBXYy1qZ20tT3loeXNjWkJmSWF5bzNXTTgyVnp5Z0N2T3NYTEJDTGJaMTk2ZjFQWFhOTkZXOHVpdUNCc2pMZzNHNzBEQ2NLWm5jOHRkaFdSTFdremNXYnE3dGNBYWQ4Mk1sVnBJMEczdEdKQU9RN3RraU1ZSzlkRThfS2hEUURPODFqTEctT0xJSGgtLWszYnho?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1670,52 +1670,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46140.29723379629</v>
+        <v>46140.59952546296</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Il 25 Aprile di Milano finisce in tribunale: denunce incrociate tra Anpi e Comunità ebraica - Affaritaliani</t>
+          <t>Correspondents' Dinner shooting suspect’s brother reported alleged manifesto to New London police - WTNH.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>On April 25th in Milan he ends up in court: cross-complaints between Anpi and the Jewish Community - Affaritaliani</t>
+          <t>Correspondents' Dinner shooting suspect’s brother reported alleged manifesto to New London police - WTNH.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 09:27:27 GMT</t>
+          <t>Tue, 28 Apr 2026 13:33:21 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQZEtWN1g0Y0JaSTllUUMwMDZ2U0hJY3QyT3BkVUlfNzJIaU8zb3BXQXQxQ2RNd0xTdDNwd19ZV21FUEdIZER0UHMzWGFpbUl2MDlfTmVxQUZjN2tvVi1Cbk5yQzA3WlpLYzZBR2U4QlVQSmYxMFJoclNhc0ZhYlkxU0JtZmRNMUdlSzlaRGNwd0hRVGU3eEF2dXQxM19xQzhTZmpuZmhrSjU1RlRvZ3hydHRUOGZrRFB1eTdFR1VBMG9yV0NKZFdfQzVtbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOX0xRZE1xSVFvZ0RXS0xITmlId0t4ZnZhcmp4eG5KT3FJVjFScThQYVo2SWtUQkxINUxZWFc4Rkx1dDdxNS10bWVnNnk0eTZXb3l5d0dSMjRfbVAtQXkya2xfeFJiQkIzeDVIOTZqLVNIMW9udlRVUldlNG44eF93WlVfN2kyVWQ0MVlJVWVFLW93UzFhNGxPaHFocV81bmdrOE5kaDlqQmNURHJVdlYwZmdwYTVXYVNsWi05dmlnYzUtelJqTnZKSGptSDBfNnp6QXBtZzRudDA?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1725,52 +1725,52 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46140.3940625</v>
+        <v>46140.56482638889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unità e responsabilità per rilanciare il presidio ospedaliero di Rho - Prima Milano Ovest</t>
+          <t>Pro-Palestinian protesters blockade defence factory in Edinburgh - London Now</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Unity and responsibility to relaunch the Rho hospital - Prima Milano Ovest</t>
+          <t>Pro-Palestinian protesters blockade defence factory in Edinburgh - London Now</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 09:08:00 GMT</t>
+          <t>Tue, 28 Apr 2026 10:15:56 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOeExpdTRjMjlmTHlfTUpHQlVJZDIyRzlIcy1FTXRVaTFMejVvVXE4MlhEWEFTMmc1UDZQX3hhRmVmYXhrMFRKZ29uNW42MW5yZkxoYl9oZDNmb3g2Y1N1R0x4WnQzbGRpeEc5N2FucnBuYU9waERXaFROMTdoeEVLeVZqdXZvTUJyZUlNLTRLeXc2RGFmOUdmS3FaSUxFVHo1RmV5aWJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGhRS2pSRTBfV254VWxvdXc1UEsxbHAxdVVsbHlhLXJQd1ZYTEU0QjNDcm9DRF9tZ0RkeUxQWHBGd0dDMkZKRFZhR3Ztdk1OQ1pGazJqSXJ5VUFrcFlyM0VVeUhyUGV0YUtQbXZwOWtQSV9JU3h1d1BWLW42dDJWd1Vxdm80d3NMdnNZM1Z0UVBtSHRqakNlNHE5MDNueU80UmlubUJkSEhIZXpReGYzU0tVNnA?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,52 +1780,52 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46140.38055555556</v>
+        <v>46140.42773148148</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maggio 2026, il mese nero per trasporti e scuole: le date critiche da segnare subito sul calendario per non rovinare viaggi ed esami - Studenti.it</t>
+          <t>Lambton College shooting suspect surrenders after police standoff in London, Ont. - Global News</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>May 2026, the black month for transport and schools: the critical dates to mark on the calendar immediately so as not to ruin trips and exams - Studenti.it</t>
+          <t>Lambton College shooting suspect surrenders after police standoff in London, Ont. - Global News</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 09:29:00 GMT</t>
+          <t>Tue, 28 Apr 2026 13:40:17 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPd2xfZlluTnBkVHdKRU9IbldERU5PRnJ4S2d6eFQ1S0JOZmRTbWZHMVlxdTFGdzd0czFPZVRKWFVKNDJPdm52VlBFb0ZXeVZ3bW4xcDdKbG56RlV5dEpNQkJJWHVaSWJYVmk0dkxkSllQRWxhR1JpUUwzaEIwUzkwUVVBcDdtcGdJN0ZjTnUwQlZDYVJlcXpkaWcwSHNZQjR2TEZxM0I1VG9OdFBBa2JGZ190NVFxdHo5STIxb0xUcTNyMnlYaFNxUEl0Z0FwaWFiT2lsYnlKOUhsb0Y2N05mM0pldlJubk9oTUhTcmNNaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBtQ0g0MWM2UDdraDhDWUVld0tDd0ZrdnF3WXh5RUVfZFNmc3llMlJONlNrUWZrYkprV29FNkMzaElELXJRakxlNGQtemoyb1V4WWEwLXNDemRteVRvYkxqU0ZrZ3ZWbmNJRHQ4?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1835,21 +1835,21 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46140.39513888889</v>
+        <v>46140.56964120371</v>
       </c>
     </row>
     <row r="27">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sgombero tendopoli Annunziata a Bologna, il parroco: "Ci sentiamo orfani" - Il Resto del Carlino</t>
+          <t>Il 25 Aprile di Milano finisce in tribunale: denunce incrociate tra Anpi e Comunità ebraica - Affaritaliani</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Clearance of Annunziata tent city in Bologna, the parish priest: "We feel like orphans" - Il Resto del Carlino</t>
+          <t>On April 25th in Milan he ends up in court: cross-complaints between Anpi and the Jewish Community - Affaritaliani</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tue, 28 Apr 2026 10:35:01 GMT</t>
+          <t>Tue, 28 Apr 2026 09:27:27 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRUN6bW1kcmpoalpzQWJzRkdSWnFXdHRBR1RMbFVmYlJsZmIxVDBJNk16OEJldS1aWVZtaVByZEh5dkxTUnVhdnNIbFpUdTJ2eFBKa0NoRHlsd1E1cE4xQVFHZUdTMUFDbDEyM1NhRXV3d2xRLUtQY1E3WUNoWS1Ed24tVUMwSldzSC1nMkJIcVVoWWE5aHZmWF9lUDd6cWdUY3FFMXdwcjJfQnZyZzQ3a016dzBzNm9I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQZEtWN1g0Y0JaSTllUUMwMDZ2U0hJY3QyT3BkVUlfNzJIaU8zb3BXQXQxQ2RNd0xTdDNwd19ZV21FUEdIZER0UHMzWGFpbUl2MDlfTmVxQUZjN2tvVi1Cbk5yQzA3WlpLYzZBR2U4QlVQSmYxMFJoclNhc0ZhYlkxU0JtZmRNMUdlSzlaRGNwd0hRVGU3eEF2dXQxM19xQzhTZmpuZmhrSjU1RlRvZ3hydHRUOGZrRFB1eTdFR1VBMG9yV0NKZFdfQzVtbw?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,7 +1904,1052 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46140.4409837963</v>
+        <v>46140.3940625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unità e responsabilità per rilanciare il presidio ospedaliero di Rho - Prima Milano Ovest</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unity and responsibility to relaunch the Rho hospital - Prima Milano Ovest</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOeExpdTRjMjlmTHlfTUpHQlVJZDIyRzlIcy1FTXRVaTFMejVvVXE4MlhEWEFTMmc1UDZQX3hhRmVmYXhrMFRKZ29uNW42MW5yZkxoYl9oZDNmb3g2Y1N1R0x4WnQzbGRpeEc5N2FucnBuYU9waERXaFROMTdoeEVLeVZqdXZvTUJyZUlNLTRLeXc2RGFmOUdmS3FaSUxFVHo1RmV5aWJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>46140.38055555556</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Milano, Brigata Ebraica: non rinunceremo al corteo - agenziagiornalisticaopinione.it</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Milan, Jewish Brigade: we will not give up on the march - agenziagiornalisticaeconomia.it</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 14:55:21 GMT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOeERpVGcyVzdPOHlJbnBaS2lxalhySTlLTlMwZUd6Ty1uUkFqTURIM2JlQWZ1b1lOd2dINF9XS2tEZ2QzWHotZWdCeWJPVUVFR3VsUEM4LTJFZkJsSVRNYWVqWUM3YVFCbVhjblk0dWVVaUdrQ2VtaVQyeWhiWUdFdDBvV29kZDhDRlh1MVFSdjZkRHQ3U2R5YzFZSUtQRk1wVUZLZTlnNkpCLUpRbHBra05qQXVUZ1R5X0JsS3lBNFYweTRmRnJ6YkRPMlVaaERaeU1WWkhzd0RJRzVidXpMTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>46140.62177083334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Maggio 2026, il mese nero per trasporti e scuole: le date critiche da segnare subito sul calendario per non rovinare viaggi ed esami - Studenti.it</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>May 2026, the black month for transport and schools: the critical dates to mark on the calendar immediately so as not to ruin trips and exams - Studenti.it</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPd2xfZlluTnBkVHdKRU9IbldERU5PRnJ4S2d6eFQ1S0JOZmRTbWZHMVlxdTFGdzd0czFPZVRKWFVKNDJPdm52VlBFb0ZXeVZ3bW4xcDdKbG56RlV5dEpNQkJJWHVaSWJYVmk0dkxkSllQRWxhR1JpUUwzaEIwUzkwUVVBcDdtcGdJN0ZjTnUwQlZDYVJlcXpkaWcwSHNZQjR2TEZxM0I1VG9OdFBBa2JGZ190NVFxdHo5STIxb0xUcTNyMnlYaFNxUEl0Z0FwaWFiT2lsYnlKOUhsb0Y2N05mM0pldlJubk9oTUhTcmNNaW0?oc=5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>46140.39513888889</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Access Disruption Maasmechelen English (fallback)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mark McKenzie Net Worth in 2026: Salary, Contract, Career Earnings - surprisesports</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mark McKenzie Net Worth in 2026: Salary, Contract, Career Earnings - surprisesports</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 14:29:48 GMT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE45MkszRHBwSzZXeGVJOFdRbE10U2RFaXBIa1JFbTRKWGZnY2xBd0xaT1VoOElzbGxUcWtkS2k3d3B1RmFpUzJET1dvd0swVllJdWVTZkVtQTBJSGpXNndZcHZRamJJYld1bV9wSlhlSm1qTHRJblQzc2tn?oc=5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>46140.60402777778</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Access Disruption Wertheim German</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "A3" OR "A81" OR "Würzburg" OR "Aschaffenburg") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz OR Verzögerung) AND -Wetter AND -Sport</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Schwerer Unfall auf der A3 bei Siershahn führt zu stundenlanger Vollsperrung - WW-Kurier</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Serious accident on the A3 near Siershahn leads to a full closure for hours - WW-Kurier</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 12:47:26 GMT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPZHprazRtQ1pCdDhIVEwtQ0cxam5QdkVTeXNQNldhdi14WkI1aVN1THhDREtvMnhELUZ5OXlrRmFMWGFrb0N1SER5WWd6TW5POUhYREZ5dXRBSmt1V1lLeVZqNDBRSHN3c1piSWhyZ0NvYXJDVUVjWGpPbjFCT3llU1ZlLTJXQWJMOHFGM0pVcU5lV2cwc0dReEtuUzV1VUFSTlpjNWpwQWFiZHZjelA4VzdmX0c0ekFh?oc=5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>DE:de</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>46140.53293981482</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Access Disruption Wertheim German</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "A3" OR "A81" OR "Würzburg" OR "Aschaffenburg") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz OR Verzögerung) AND -Wetter AND -Sport</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>27.04.: Schnelle erste Hilfe: Polizist reanimiert 70-Jährigen nach Unfall auf der A3 und rettet ihm das Leben - blick-aktuell.de</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>April 27th: Quick first aid: Police officer resuscitates 70-year-old man after accident on the A3 and saves his life - blick-aktuell.de</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 08:59:58 GMT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOYUVBNGZNWGhyQ2VMa3o5M2RqSXNWYVNfZlNGQjJ3LUNTS0JkUzlIWHYyVmNkNG1OVi00Mk9oeEpYaDdmLVZpcmRHdWlXS0RPVW5vSDQ2NDlGMGlJenBEa1hJMTFpY1haZlpSeUJXeVJzZWcxak5PcGpiYlBUeW9fQm5EcUYtLVFoTEhyc1YxbmlmX0pBaFhzU3VuM29wYjRKdE5RZU1kTURTN2E4T25OQUJ0eWZEZmIwaVdrRnBDVG1QekNqa1BLcmFyMlV0RHctcms2UHZ1MlBZdHVIcklJNzk2OFQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>DE:de</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>46140.37497685185</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Access Disruption Wertheim German</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "A3" OR "A81" OR "Würzburg" OR "Aschaffenburg") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz OR Verzögerung) AND -Wetter AND -Sport</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wertheim: Tödlicher Unfall: Mann wird in Wertheim unter eigenem Wohnmobil eingeklemmt - Main-Post</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wertheim: Fatal accident: Man is trapped under his own mobile home in Wertheim - Main-Post</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 08:19:29 GMT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxONmdBejhtSkE0YWwtYzBiT2VaUDJEOXFVREctYUdQbVdWRlQ3Qk9fMjctYmNNRDByU2pWYXo1U0J3Z2lTMkJQLW5RaVA1dm1iV05fTGxmeGh4TkowdElLVlllQjdOWkpKMnExYjBJZlhicjVDQTIyME9qdkMzY29xZmVubnhHTlQ0cVU3eFVTel9EMEowTkpfUmJQS1dEWGUtUDhqX3lXX2JOTWM2NktLMksyLVFVMDBPMnk3X3ZXZldxVVpZbHo0a0ZR?oc=5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DE:de</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>46140.34686342593</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Access Disruption Wertheim English (fallback)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Why are vintage maps the most popular artworks in the room? - The Spaces</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Why are vintage maps the most popular artworks in the room? - The Spaces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 08:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQRXFpOWg0a3JibnlwV2VPcG9TeExxaUFpUno4NG84Q1FyWUlOTDlYbWxjS0kzeUN2WkZ0R3BMcWRMNm9iVTlEWEVzekdfeGFhTTNzRlBIOGMzSVcyR3poZThfc05wSmRhRjF3Z0NXeUtGVHVvWVNrc0VwNmlFdUxoSkU3WFQ1ZGtq?oc=5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>46140.3359375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Access Disruption Wertheim English (fallback)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dung beetles have a tough life. Climate change is making it worse - MSN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Dung beetles have a tough life. Climate change is making it worse - MSN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 08:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wJBVV95cUxQdklnUjFzblBTNmhMVDEwWGV0bUo3eWVaLUN4S3VFcUZKLUdseDlBVmxCRWZiSFpPME1QMTE0ZjVYZUxtR29VTEVrdzF6emV1MUJteDJSaFU4aVVPYlNTbXZfSk5idUI1U2g0dXRUcnFNMWZMVmlRaUJOSk1kQXVCQVRDaU45M0xBNHdyZ1dNSU5UTFh6dzRISlpjNk43MlV1WjFGcFhvY0lESEZHcUo0UDdyOTRDdjBqUDhUaWdLa2l3eEZucWdLSXFZMlZ5cWVFMGROSnhxbWtuT0FOblZPdnFKUi1KaFlNd2JDQTBrSl9HVmlrcUNuRVNUMndPV2NzOWdBRUwzS2FnS2VTbDVzd2dvZVhGemI5R2JlOE0zZDZVMmh4bkp6b3VCZU83UGRHWE4yQV9qRk9USzBnYzNoTEZxeHFuNjNYekJKR1lsUXZvejZxM2RybERrNE05Z3YxcGdOdUtlc1hFTkxPZTQtd0lzd2VtMVU?oc=5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>46140.36111111111</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Access Disruption Ingolstadt German</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Frau stirbt nach Frontalzusammenstoß auf der B9 bei Kevelaer - MSN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Woman dies after head-on collision on the B9 near Kevelaer - MSN</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:37:16 GMT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AJBVV95cUxNY2N5RUR4WVY5M0VySXQ4WU1IcnJzYWhiVlNkaDd4cWpwRUd3QWxzYTljT0xlSGZYWU9fNEF4QXgwUjU3MzJfTExLZnBhRnU2SG1zX1JoTktNRmFkblVPbW4yRGUyTF9hNTRZQ1FzaXJzVk8wa0VyUUIxUUxkYW9VS0JwMjVfamszUGV3RjlIUW93ZDF2WVUwaWpCdmh3WlZBNVpWaTJVLXZDVHZJbUVIZVVNSjJlZjJMczJ2am1mV0NXSlZZRzZRTWMzZ3JnVXMza2tJdFVsZ2gyMTJkRTc4eUJyNUhZdWdaamFmX0VQaURsZl9QN1dXMEZDUXE0VzVRejRIeXJCQkJ4TV92WUZhNGd3eFQ2MlVnQkRmUWpRN3FDNElfOXM3dXJhRV90WHRUZHBtc2RfdTlwM1lHT3N2UTQ5NERxUFVDVWI1czVYMzJkRXg2WXlRLURyNUJqS0hWZmFFYWpkdWIzN0Ff?oc=5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DE:de</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>46140.40087962963</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Access Disruption Ingolstadt German</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Volle Straßen zum 1. Mai: Wo Reisende am langen Wochenende mit Staus rechnen müssen - Reisereporter</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Full streets on May 1st: Where travelers have to expect traffic jams on the long weekend - travel reporter</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 13:26:40 GMT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQZHdtN2tHb3BtU2c0cTZ5eUNMQWJudE9JUFZfcWQyY2sybFVJd0tYanlpakdvb3FGb09yMmpzeFhhVWlJb3J1ZFIxejZ6ZFZaVmNqaTJYNzhsWGlWN2VoXzZja3k0V2FDTjRlZWcxRFBRQk5oMDV3UXVNVmZoMWFaUi1HTUVNZ21sZVpIZVhKQXphZ05FbWxPbURvYTc0TEcxTS1TWkplcFN1WkprNGpEUmhlV1ZZVzNFX1RZZk8wTHhrU1lxNWtjYTFibFlDUGQ5bU81RVpQUk1UQU90bHhfMGRTbzBiWnQyLUHSAYYCQVVfeXFMTU9fUDFJWUptSkhmVTVUX3RLX1BaQTBxcS1UU2d2Sk1VLWlrUENDXzZUaDZrR2ZHLXJFMjJDTU9sSV9ZTzNKXzhIWUtMZktYQXE1LVZfc3lPdTVYU19uY2VjSmp5cDFBOWFsU3N0MHBDNUktYWxPZzZkaFdEZFFzeDdrUlg4Tk5HT3BhRWlacEVOOE9pOWJSU2V3djBVdjVwRVRRZENPbXdqTlE5NUo0c1VEVGZncXM0OHYxa3dqTVFTN0F5QXQtUmk0Y3lUWlhTOWVKbWxqZmN2aVVVRF9oMjdpd1ktX1htNmlnNy11bHlYa1V2RkVUR0tJZjF5RWYxVlEzQm94UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DE:de</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>46140.56018518518</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Marotta, incidente in autostrada: traffico bloccato, 4 km di coda - eTv Marche</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Marotta, accident on the motorway: traffic blocked, 4 km queue - eTv Marche</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 13:04:47 GMT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWVhsSTlLOVNDX3M2aWlLVldqejczQ3RhSlJvSlVpR3FDeC11SWJnTzNGRjU3T1lmeldwMGFFa2NXbFZCZl94WmtYeURpUjlLUFg3R20xY2NhU1ZUMnhydXlhSnVkRURVRWJVd3ozT2E1S2I1N3FqWGFHYklkQXJvM2tDLV8tcDFuVUR0dWliUW56U011S3dyOWdfNA?oc=5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>46140.54498842593</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A14 Fano-Marotta: incidente tra tre camion, traffico bloccato - Occhio alla Notizia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A14 Fano-Marotta: accident between three trucks, traffic blocked - Watch out for the news</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 12:32:58 GMT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQTEdfblA4ekh0cGVNYlh6WGV1cHRUYWxVMGpTRGluN1JZWWp5T0poZkl2MHNFT1RNWUNLSmhuS3IxQ0lRbjVKdlAwdEd3bHBROWRONXB3dHBCN3pOU2FVakJJUml2VmJZN1l0MEh1bHUyRnIzOHd5SVZNMXB0M3duSG40Uy1vc1RTWTdQR1RnVTJnVjNabk11OA?oc=5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>46140.52289351852</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Incidente a Parma: studentessa cade dalle scale a scuola, è grave - Scuolalink</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Accident in Parma: student falls down the stairs at school, it's serious - Scuolalink</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQSXZ4UWdZMUlxVGdpNlh6eVlyR2hhT0VZVy1xajdXeGJ0UEFDamU4eGh1V3lYblVidzBjV2E0OXZIOVRiVV8yRHRkbndXWnR3YzV1Nm1iTHBHQWx2WmxueV9rZGZwVXRrTHZyZmtHa0p4bjdrRDRYNjdGXzZ6bm5zcGRTdFpZZzZkZEtVVGFOZWV3Njg?oc=5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>46140.41666666666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Autostrade, allerta Anac al Ministero: «Gare in ritardo, così favorisci i gestori» - Il Giornale di Vicenza</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Motorways, Anac alerts the Ministry: «Delayed tenders, thus favoring the managers» - Il Giornale di Vicenza</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:59:34 GMT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZHEzRHdqbjVteUVCOFBJZHFQZUt0b0lxMUNaTkRXR2V3M0dqdzhuT3VWX2xYd2xaUUdGa3U4c254SU15Tk9NOXUzd1d2azNZODd3ckJrR1RKb3lDNmw3SEJ6Q0dHcjlRdlByanRhRk9RUkdlLWJsT2VKR21kd01SSWRGekVrN21JU0Q1Q0ZkNTBkSk0xLTVXdHZzMHF6TnNZdko3YkZIRks0d0xFS2FocDl4R1J6WXBZS0lVeHlPb3p5YjhEZHFsV0NvYmNsS0RMNHdyZDV30gHWAUFVX3lxTE9kcTNEd2puNW15RUI4UElkcVBlS3RvSXExQ1pORFdHZXczR2p3OG5PdVZfbFh3bFpRR0ZrdThzbnhJTXlOT005dTN3V3ZrM1k4N3dyQmtHVEpveUM2bDdIQnpDR0dyOVF2UHJqdGFGT1FSR2UtYmxPZUpHbWR3TVJJZEZ6RWs3bUlTRDVDRmQ1MGRKTTEtNVd0dnMwcXpOc1l2SjdiRkhGSzR3TEVLYWhwOXhHUnpZcFlLSVV4eU9venliOERkcWxXQ29iY2xLREw0d3JkNXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>46140.41636574074</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Incidente in moto sul ponte per Viadana: grave un 50enne di Poviglio - Gazzetta di Reggio</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Motorcycle accident on the bridge to Viadana: a 50-year-old from Poviglio is seriously injured - Gazzetta di Reggio</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 14:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPRWNzTExETmIxek5KMzV6cldJMVBTZ3VXN1NXaDRzaGxRWGxjUEVYaHNFV3lhVUJQcFhTQ3h0RlhzWTFNSkY1eXF0cmJTVkdXYTJPVnFENHBxdDVmQWc4SFF5XzNzN25KdkZaS1hoYkFjYzNpMUNCQnE1REx3cHNaZU5jaEhhaFIyREtsWF95LXdnTmVqR1AydFMyOFU1eUhsNmpJUDFBV1F2SDh0ZkF5a1FEaGVZSk41R1JMbzdIdWhkVkY5anNqNVNvVVh0S0pQXzgwOFM5ay1Sdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>46140.62291666667</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Incidente sull’A14 tra Fano e Marotta: code e acqua distribuita agli automobilisti - Occhio alla Notizia</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Accident on the A14 between Fano and Marotta: queues and water distributed to motorists - Watch out for the news</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 12:32:58 GMT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOR0Q4SlRrc1JQZmdtRWJLVUl6XzkzNGF5WmlMLUhpV2lSS1U3bjMyMzg2em1reEZjbUg3SjhZcWhESkhQcV9mSFVQRE85S2J1MF9NUENnbGZaMzBQWXFaUUxDVFZELWlpMFBVbnk0eFE3UzIwVzNueFkxT3NmRGJkUXdfeVk3d2Q4VjZDRHB3Q3pMTFlaRmg4M2RlUElqWnk1WnkyZkRlU2hFdXFOd1laRHZvcjI?oc=5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>46140.52289351852</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Incidente sulla A19: Tir carico d’acqua si ribalta a Gerbini, traffico in tilt verso Catania - ViviEnna</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Accident on the A19: Truck full of water overturns in Gerbini, traffic in disarray towards Catania - ViviEnna</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 09:42:30 GMT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVDN3MUZPb3JkVXFmcExreWROVTB3ZldEbVVoeTBlV2xHSTAya3ZCcXllQXZCQ2doMVdWblpDS3RuZ3pkSkVVckVfWkMxbGZYTmI3N0FaSHhDUnU4SUl3ZENPYnVtbV9jd2VxSnU2c0lFSGt4RHVJWEhGcUhiT3lidW10Ml91NzJnNjk3YmhDUEE2VVhHZ29mQndjbzdYcnRUdEROcDFnYk5xdWFPelYtNjU5TDlHQUhqTkRNZXVna2trYWM?oc=5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>46140.40451388889</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Access Disruption Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Taser a scuola, il caso di Parma: studenti si difendono dai furti fuori dagli istituti - newsistruzione.it</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Taser at school, the case of Parma: students defend themselves from thefts outside schools - newsformazione.it</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 11:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPY0FDODMtQ3BWTGoxZjFNejQ2eTRJRFppNThIWVMxbnUzRnR4c3kxa1J4aGhodzAzaEJVQV9OYURIVlZ4bnVnaGdadERZSldlM1ZkZkgwVTN3V1VvZ01nY1Vzb0NLRmtBWFZsNjRPTWJVdkRfemtOdlQ4MGFEal9DVFp4RjFWc2FJWVBOQ3Fhd2x2dTlIRFBtaENab1dYeW1IYk5hNzFMSjBOVzRJZWJfdW1iSnBIQzNNN3N4ei1MVnZTdzDSAcgBQVVfeXFMUDRlMkdkb3Fhb0FSSFY5TkdYOXJ6TWlEVnN2T0N6Qmc2STlyUWloNF9kQXdyTzdzT1RxSFZDZVdrV2VUQk9YbVQ3WWJHejlLZnFPVHJHNFFXZnBnSldFLXByZ2E3M0JzOTAxZkVyRTJjTW9sNFYwRWZMZVpUUHpMd25PS3puSnl2UUVUM0dvVEtMYTFiOWw5MU9ZcHBGeTdPNkhGb2lVTkVrd2FWdWttRzdKbmhDcjRPNUVxUG5iSXA2SlNGYU5iams?oc=5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>46140.45833333334</v>
       </c>
     </row>
   </sheetData>
